--- a/해주오씨_지군사공파_전체_족보_통합_v16_DB.xlsx
+++ b/해주오씨_지군사공파_전체_족보_통합_v16_DB.xlsx
@@ -2,24 +2,23 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="지군사공파_통합_v16_DB" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -27,13 +26,24 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -45,20 +55,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F497D"/>
-        <bgColor rgb="001F497D"/>
+        <fgColor rgb="FF1F497D"/>
+        <bgColor rgb="FF1F497D"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-        <bgColor rgb="00E2EFDA"/>
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-        <bgColor rgb="00F2F2F2"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -72,17 +82,18 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D9D9D9"/>
+        <color rgb="FFD9D9D9"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -107,7 +118,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -471,24 +482,21 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:P546"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
-    <col width="13.2" customWidth="1" min="1" max="1"/>
-    <col width="13.2" customWidth="1" min="2" max="2"/>
+    <col width="13.25" customWidth="1" min="1" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="20.2" customWidth="1" min="4" max="4"/>
-    <col width="13.2" customWidth="1" min="5" max="5"/>
+    <col width="20.25" customWidth="1" min="4" max="4"/>
+    <col width="13.25" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="50" customWidth="1" min="8" max="10"/>
     <col width="37" customWidth="1" min="11" max="11"/>
-    <col width="17.4" customWidth="1" min="12" max="12"/>
-    <col width="25.8" customWidth="1" min="13" max="13"/>
-    <col width="32.8" customWidth="1" min="14" max="14"/>
+    <col width="17.375" customWidth="1" min="12" max="12"/>
+    <col width="25.75" customWidth="1" min="13" max="13"/>
+    <col width="32.75" customWidth="1" min="14" max="14"/>
     <col width="50" customWidth="1" min="15" max="15"/>
-    <col width="28.6" customWidth="1" min="16" max="16"/>
+    <col width="28.625" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -611,7 +619,7 @@
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>1세계보도仁裕(인유)高麗檢校軍器監監丁卯一九八七年四月十二日(陰三月十五日)設壇于京畿道龍仁市處仁區慕賢邑吳山里四五名曰始祖壇每年陰三月十五日行享祀</t>
+          <t>시조 仁裕(인유) 高麗檢校軍器監監丁卯一九八七年四月十二日(陰三月十五日)設壇于京畿道龍仁市處仁區慕賢邑吳山里四五名曰始祖壇每年陰三月十五日行享祀</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -803,8 +811,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="3" t="inlineStr"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="3" t="n"/>
       <c r="P4" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -877,8 +885,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
+      <c r="N5" s="2" t="n"/>
+      <c r="O5" s="3" t="n"/>
       <c r="P5" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -1033,8 +1041,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr"/>
+      <c r="N7" s="2" t="n"/>
+      <c r="O7" s="3" t="n"/>
       <c r="P7" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -1271,8 +1279,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="3" t="inlineStr"/>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="3" t="n"/>
       <c r="P10" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -2001,8 +2009,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N19" s="2" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr"/>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="3" t="n"/>
       <c r="P19" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -2321,8 +2329,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N23" s="2" t="inlineStr"/>
-      <c r="O23" s="3" t="inlineStr"/>
+      <c r="N23" s="2" t="n"/>
+      <c r="O23" s="3" t="n"/>
       <c r="P23" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -2641,8 +2649,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N27" s="2" t="inlineStr"/>
-      <c r="O27" s="3" t="inlineStr"/>
+      <c r="N27" s="2" t="n"/>
+      <c r="O27" s="3" t="n"/>
       <c r="P27" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -2797,8 +2805,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N29" s="2" t="inlineStr"/>
-      <c r="O29" s="3" t="inlineStr"/>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="3" t="n"/>
       <c r="P29" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -2871,8 +2879,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N30" s="2" t="inlineStr"/>
-      <c r="O30" s="3" t="inlineStr"/>
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="3" t="n"/>
       <c r="P30" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -2945,8 +2953,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N31" s="2" t="inlineStr"/>
-      <c r="O31" s="3" t="inlineStr"/>
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="3" t="n"/>
       <c r="P31" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -3019,8 +3027,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="3" t="inlineStr"/>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="3" t="n"/>
       <c r="P32" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -3093,8 +3101,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N33" s="2" t="inlineStr"/>
-      <c r="O33" s="3" t="inlineStr"/>
+      <c r="N33" s="2" t="n"/>
+      <c r="O33" s="3" t="n"/>
       <c r="P33" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -3167,8 +3175,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="3" t="inlineStr"/>
+      <c r="N34" s="2" t="n"/>
+      <c r="O34" s="3" t="n"/>
       <c r="P34" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -3241,8 +3249,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N35" s="2" t="inlineStr"/>
-      <c r="O35" s="3" t="inlineStr"/>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="3" t="n"/>
       <c r="P35" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -3315,8 +3323,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N36" s="2" t="inlineStr"/>
-      <c r="O36" s="3" t="inlineStr"/>
+      <c r="N36" s="2" t="n"/>
+      <c r="O36" s="3" t="n"/>
       <c r="P36" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -3389,8 +3397,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N37" s="2" t="inlineStr"/>
-      <c r="O37" s="3" t="inlineStr"/>
+      <c r="N37" s="2" t="n"/>
+      <c r="O37" s="3" t="n"/>
       <c r="P37" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -3463,8 +3471,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N38" s="2" t="inlineStr"/>
-      <c r="O38" s="3" t="inlineStr"/>
+      <c r="N38" s="2" t="n"/>
+      <c r="O38" s="3" t="n"/>
       <c r="P38" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -3537,8 +3545,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N39" s="2" t="inlineStr"/>
-      <c r="O39" s="3" t="inlineStr"/>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="3" t="n"/>
       <c r="P39" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -3611,8 +3619,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N40" s="2" t="inlineStr"/>
-      <c r="O40" s="3" t="inlineStr"/>
+      <c r="N40" s="2" t="n"/>
+      <c r="O40" s="3" t="n"/>
       <c r="P40" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -3685,8 +3693,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N41" s="2" t="inlineStr"/>
-      <c r="O41" s="3" t="inlineStr"/>
+      <c r="N41" s="2" t="n"/>
+      <c r="O41" s="3" t="n"/>
       <c r="P41" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -3841,8 +3849,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N43" s="2" t="inlineStr"/>
-      <c r="O43" s="3" t="inlineStr"/>
+      <c r="N43" s="2" t="n"/>
+      <c r="O43" s="3" t="n"/>
       <c r="P43" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -3915,8 +3923,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N44" s="2" t="inlineStr"/>
-      <c r="O44" s="3" t="inlineStr"/>
+      <c r="N44" s="2" t="n"/>
+      <c r="O44" s="3" t="n"/>
       <c r="P44" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -3989,8 +3997,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N45" s="2" t="inlineStr"/>
-      <c r="O45" s="3" t="inlineStr"/>
+      <c r="N45" s="2" t="n"/>
+      <c r="O45" s="3" t="n"/>
       <c r="P45" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -4063,8 +4071,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N46" s="2" t="inlineStr"/>
-      <c r="O46" s="3" t="inlineStr"/>
+      <c r="N46" s="2" t="n"/>
+      <c r="O46" s="3" t="n"/>
       <c r="P46" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -4137,8 +4145,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N47" s="2" t="inlineStr"/>
-      <c r="O47" s="3" t="inlineStr"/>
+      <c r="N47" s="2" t="n"/>
+      <c r="O47" s="3" t="n"/>
       <c r="P47" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -4293,8 +4301,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N49" s="2" t="inlineStr"/>
-      <c r="O49" s="3" t="inlineStr"/>
+      <c r="N49" s="2" t="n"/>
+      <c r="O49" s="3" t="n"/>
       <c r="P49" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -4449,8 +4457,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N51" s="2" t="inlineStr"/>
-      <c r="O51" s="3" t="inlineStr"/>
+      <c r="N51" s="2" t="n"/>
+      <c r="O51" s="3" t="n"/>
       <c r="P51" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -4523,8 +4531,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N52" s="2" t="inlineStr"/>
-      <c r="O52" s="3" t="inlineStr"/>
+      <c r="N52" s="2" t="n"/>
+      <c r="O52" s="3" t="n"/>
       <c r="P52" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -4597,8 +4605,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N53" s="2" t="inlineStr"/>
-      <c r="O53" s="3" t="inlineStr"/>
+      <c r="N53" s="2" t="n"/>
+      <c r="O53" s="3" t="n"/>
       <c r="P53" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -4671,8 +4679,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N54" s="2" t="inlineStr"/>
-      <c r="O54" s="3" t="inlineStr"/>
+      <c r="N54" s="2" t="n"/>
+      <c r="O54" s="3" t="n"/>
       <c r="P54" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -4745,8 +4753,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N55" s="2" t="inlineStr"/>
-      <c r="O55" s="3" t="inlineStr"/>
+      <c r="N55" s="2" t="n"/>
+      <c r="O55" s="3" t="n"/>
       <c r="P55" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -4819,8 +4827,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N56" s="2" t="inlineStr"/>
-      <c r="O56" s="3" t="inlineStr"/>
+      <c r="N56" s="2" t="n"/>
+      <c r="O56" s="3" t="n"/>
       <c r="P56" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -4893,8 +4901,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N57" s="2" t="inlineStr"/>
-      <c r="O57" s="3" t="inlineStr"/>
+      <c r="N57" s="2" t="n"/>
+      <c r="O57" s="3" t="n"/>
       <c r="P57" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -4967,8 +4975,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N58" s="2" t="inlineStr"/>
-      <c r="O58" s="3" t="inlineStr"/>
+      <c r="N58" s="2" t="n"/>
+      <c r="O58" s="3" t="n"/>
       <c r="P58" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -5041,8 +5049,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N59" s="2" t="inlineStr"/>
-      <c r="O59" s="3" t="inlineStr"/>
+      <c r="N59" s="2" t="n"/>
+      <c r="O59" s="3" t="n"/>
       <c r="P59" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -5115,8 +5123,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N60" s="2" t="inlineStr"/>
-      <c r="O60" s="3" t="inlineStr"/>
+      <c r="N60" s="2" t="n"/>
+      <c r="O60" s="3" t="n"/>
       <c r="P60" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -5189,8 +5197,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N61" s="2" t="inlineStr"/>
-      <c r="O61" s="3" t="inlineStr"/>
+      <c r="N61" s="2" t="n"/>
+      <c r="O61" s="3" t="n"/>
       <c r="P61" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -5263,8 +5271,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N62" s="2" t="inlineStr"/>
-      <c r="O62" s="3" t="inlineStr"/>
+      <c r="N62" s="2" t="n"/>
+      <c r="O62" s="3" t="n"/>
       <c r="P62" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -5337,8 +5345,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N63" s="2" t="inlineStr"/>
-      <c r="O63" s="3" t="inlineStr"/>
+      <c r="N63" s="2" t="n"/>
+      <c r="O63" s="3" t="n"/>
       <c r="P63" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -5411,8 +5419,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N64" s="2" t="inlineStr"/>
-      <c r="O64" s="3" t="inlineStr"/>
+      <c r="N64" s="2" t="n"/>
+      <c r="O64" s="3" t="n"/>
       <c r="P64" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -5485,8 +5493,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N65" s="2" t="inlineStr"/>
-      <c r="O65" s="3" t="inlineStr"/>
+      <c r="N65" s="2" t="n"/>
+      <c r="O65" s="3" t="n"/>
       <c r="P65" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -5559,8 +5567,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N66" s="2" t="inlineStr"/>
-      <c r="O66" s="3" t="inlineStr"/>
+      <c r="N66" s="2" t="n"/>
+      <c r="O66" s="3" t="n"/>
       <c r="P66" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -5633,8 +5641,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N67" s="2" t="inlineStr"/>
-      <c r="O67" s="3" t="inlineStr"/>
+      <c r="N67" s="2" t="n"/>
+      <c r="O67" s="3" t="n"/>
       <c r="P67" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -5707,8 +5715,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N68" s="2" t="inlineStr"/>
-      <c r="O68" s="3" t="inlineStr"/>
+      <c r="N68" s="2" t="n"/>
+      <c r="O68" s="3" t="n"/>
       <c r="P68" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -5781,8 +5789,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N69" s="2" t="inlineStr"/>
-      <c r="O69" s="3" t="inlineStr"/>
+      <c r="N69" s="2" t="n"/>
+      <c r="O69" s="3" t="n"/>
       <c r="P69" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -5855,8 +5863,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N70" s="2" t="inlineStr"/>
-      <c r="O70" s="3" t="inlineStr"/>
+      <c r="N70" s="2" t="n"/>
+      <c r="O70" s="3" t="n"/>
       <c r="P70" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -5929,8 +5937,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N71" s="2" t="inlineStr"/>
-      <c r="O71" s="3" t="inlineStr"/>
+      <c r="N71" s="2" t="n"/>
+      <c r="O71" s="3" t="n"/>
       <c r="P71" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -6003,8 +6011,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N72" s="2" t="inlineStr"/>
-      <c r="O72" s="3" t="inlineStr"/>
+      <c r="N72" s="2" t="n"/>
+      <c r="O72" s="3" t="n"/>
       <c r="P72" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -6159,8 +6167,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N74" s="2" t="inlineStr"/>
-      <c r="O74" s="3" t="inlineStr"/>
+      <c r="N74" s="2" t="n"/>
+      <c r="O74" s="3" t="n"/>
       <c r="P74" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -6233,8 +6241,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N75" s="2" t="inlineStr"/>
-      <c r="O75" s="3" t="inlineStr"/>
+      <c r="N75" s="2" t="n"/>
+      <c r="O75" s="3" t="n"/>
       <c r="P75" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -6307,8 +6315,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N76" s="2" t="inlineStr"/>
-      <c r="O76" s="3" t="inlineStr"/>
+      <c r="N76" s="2" t="n"/>
+      <c r="O76" s="3" t="n"/>
       <c r="P76" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -6381,8 +6389,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N77" s="2" t="inlineStr"/>
-      <c r="O77" s="3" t="inlineStr"/>
+      <c r="N77" s="2" t="n"/>
+      <c r="O77" s="3" t="n"/>
       <c r="P77" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -6455,8 +6463,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N78" s="2" t="inlineStr"/>
-      <c r="O78" s="3" t="inlineStr"/>
+      <c r="N78" s="2" t="n"/>
+      <c r="O78" s="3" t="n"/>
       <c r="P78" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -6529,8 +6537,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N79" s="2" t="inlineStr"/>
-      <c r="O79" s="3" t="inlineStr"/>
+      <c r="N79" s="2" t="n"/>
+      <c r="O79" s="3" t="n"/>
       <c r="P79" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -6603,8 +6611,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N80" s="2" t="inlineStr"/>
-      <c r="O80" s="3" t="inlineStr"/>
+      <c r="N80" s="2" t="n"/>
+      <c r="O80" s="3" t="n"/>
       <c r="P80" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -6677,8 +6685,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N81" s="2" t="inlineStr"/>
-      <c r="O81" s="3" t="inlineStr"/>
+      <c r="N81" s="2" t="n"/>
+      <c r="O81" s="3" t="n"/>
       <c r="P81" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -6751,8 +6759,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N82" s="2" t="inlineStr"/>
-      <c r="O82" s="3" t="inlineStr"/>
+      <c r="N82" s="2" t="n"/>
+      <c r="O82" s="3" t="n"/>
       <c r="P82" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -6825,8 +6833,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N83" s="2" t="inlineStr"/>
-      <c r="O83" s="3" t="inlineStr"/>
+      <c r="N83" s="2" t="n"/>
+      <c r="O83" s="3" t="n"/>
       <c r="P83" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -7227,8 +7235,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N88" s="2" t="inlineStr"/>
-      <c r="O88" s="3" t="inlineStr"/>
+      <c r="N88" s="2" t="n"/>
+      <c r="O88" s="3" t="n"/>
       <c r="P88" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -7301,8 +7309,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N89" s="2" t="inlineStr"/>
-      <c r="O89" s="3" t="inlineStr"/>
+      <c r="N89" s="2" t="n"/>
+      <c r="O89" s="3" t="n"/>
       <c r="P89" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -7785,8 +7793,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N95" s="2" t="inlineStr"/>
-      <c r="O95" s="3" t="inlineStr"/>
+      <c r="N95" s="2" t="n"/>
+      <c r="O95" s="3" t="n"/>
       <c r="P95" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -7859,8 +7867,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N96" s="2" t="inlineStr"/>
-      <c r="O96" s="3" t="inlineStr"/>
+      <c r="N96" s="2" t="n"/>
+      <c r="O96" s="3" t="n"/>
       <c r="P96" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -8097,8 +8105,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N99" s="2" t="inlineStr"/>
-      <c r="O99" s="3" t="inlineStr"/>
+      <c r="N99" s="2" t="n"/>
+      <c r="O99" s="3" t="n"/>
       <c r="P99" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -8171,8 +8179,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N100" s="2" t="inlineStr"/>
-      <c r="O100" s="3" t="inlineStr"/>
+      <c r="N100" s="2" t="n"/>
+      <c r="O100" s="3" t="n"/>
       <c r="P100" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -8491,8 +8499,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N104" s="2" t="inlineStr"/>
-      <c r="O104" s="3" t="inlineStr"/>
+      <c r="N104" s="2" t="n"/>
+      <c r="O104" s="3" t="n"/>
       <c r="P104" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -8565,8 +8573,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N105" s="2" t="inlineStr"/>
-      <c r="O105" s="3" t="inlineStr"/>
+      <c r="N105" s="2" t="n"/>
+      <c r="O105" s="3" t="n"/>
       <c r="P105" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -8639,8 +8647,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N106" s="2" t="inlineStr"/>
-      <c r="O106" s="3" t="inlineStr"/>
+      <c r="N106" s="2" t="n"/>
+      <c r="O106" s="3" t="n"/>
       <c r="P106" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -8959,8 +8967,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N110" s="2" t="inlineStr"/>
-      <c r="O110" s="3" t="inlineStr"/>
+      <c r="N110" s="2" t="n"/>
+      <c r="O110" s="3" t="n"/>
       <c r="P110" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -11001,8 +11009,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N135" s="2" t="inlineStr"/>
-      <c r="O135" s="3" t="inlineStr"/>
+      <c r="N135" s="2" t="n"/>
+      <c r="O135" s="3" t="n"/>
       <c r="P135" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -12469,8 +12477,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N153" s="2" t="inlineStr"/>
-      <c r="O153" s="3" t="inlineStr"/>
+      <c r="N153" s="2" t="n"/>
+      <c r="O153" s="3" t="n"/>
       <c r="P153" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -12625,8 +12633,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N155" s="2" t="inlineStr"/>
-      <c r="O155" s="3" t="inlineStr"/>
+      <c r="N155" s="2" t="n"/>
+      <c r="O155" s="3" t="n"/>
       <c r="P155" s="5" t="inlineStr">
         <is>
           <t>주의: 동명이인 중 임의 매칭</t>
@@ -13273,8 +13281,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N163" s="2" t="inlineStr"/>
-      <c r="O163" s="3" t="inlineStr"/>
+      <c r="N163" s="2" t="n"/>
+      <c r="O163" s="3" t="n"/>
       <c r="P163" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -16217,8 +16225,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N199" s="2" t="inlineStr"/>
-      <c r="O199" s="3" t="inlineStr"/>
+      <c r="N199" s="2" t="n"/>
+      <c r="O199" s="3" t="n"/>
       <c r="P199" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -16373,8 +16381,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N201" s="2" t="inlineStr"/>
-      <c r="O201" s="3" t="inlineStr"/>
+      <c r="N201" s="2" t="n"/>
+      <c r="O201" s="3" t="n"/>
       <c r="P201" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -17677,8 +17685,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N217" s="2" t="inlineStr"/>
-      <c r="O217" s="3" t="inlineStr"/>
+      <c r="N217" s="2" t="n"/>
+      <c r="O217" s="3" t="n"/>
       <c r="P217" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -18079,8 +18087,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N222" s="2" t="inlineStr"/>
-      <c r="O222" s="3" t="inlineStr"/>
+      <c r="N222" s="2" t="n"/>
+      <c r="O222" s="3" t="n"/>
       <c r="P222" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -18809,8 +18817,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N231" s="2" t="inlineStr"/>
-      <c r="O231" s="3" t="inlineStr"/>
+      <c r="N231" s="2" t="n"/>
+      <c r="O231" s="3" t="n"/>
       <c r="P231" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -19703,8 +19711,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N242" s="2" t="inlineStr"/>
-      <c r="O242" s="3" t="inlineStr"/>
+      <c r="N242" s="2" t="n"/>
+      <c r="O242" s="3" t="n"/>
       <c r="P242" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -20515,8 +20523,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N252" s="2" t="inlineStr"/>
-      <c r="O252" s="3" t="inlineStr"/>
+      <c r="N252" s="2" t="n"/>
+      <c r="O252" s="3" t="n"/>
       <c r="P252" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -20835,8 +20843,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N256" s="2" t="inlineStr"/>
-      <c r="O256" s="3" t="inlineStr"/>
+      <c r="N256" s="2" t="n"/>
+      <c r="O256" s="3" t="n"/>
       <c r="P256" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -21401,8 +21409,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N263" s="2" t="inlineStr"/>
-      <c r="O263" s="3" t="inlineStr"/>
+      <c r="N263" s="2" t="n"/>
+      <c r="O263" s="3" t="n"/>
       <c r="P263" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -22049,8 +22057,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N271" s="2" t="inlineStr"/>
-      <c r="O271" s="3" t="inlineStr"/>
+      <c r="N271" s="2" t="n"/>
+      <c r="O271" s="3" t="n"/>
       <c r="P271" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -22205,8 +22213,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N273" s="2" t="inlineStr"/>
-      <c r="O273" s="3" t="inlineStr"/>
+      <c r="N273" s="2" t="n"/>
+      <c r="O273" s="3" t="n"/>
       <c r="P273" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -22279,8 +22287,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N274" s="2" t="inlineStr"/>
-      <c r="O274" s="3" t="inlineStr"/>
+      <c r="N274" s="2" t="n"/>
+      <c r="O274" s="3" t="n"/>
       <c r="P274" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -22845,8 +22853,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N281" s="2" t="inlineStr"/>
-      <c r="O281" s="3" t="inlineStr"/>
+      <c r="N281" s="2" t="n"/>
+      <c r="O281" s="3" t="n"/>
       <c r="P281" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -22919,8 +22927,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N282" s="2" t="inlineStr"/>
-      <c r="O282" s="3" t="inlineStr"/>
+      <c r="N282" s="2" t="n"/>
+      <c r="O282" s="3" t="n"/>
       <c r="P282" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -23075,8 +23083,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N284" s="2" t="inlineStr"/>
-      <c r="O284" s="3" t="inlineStr"/>
+      <c r="N284" s="2" t="n"/>
+      <c r="O284" s="3" t="n"/>
       <c r="P284" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -23559,8 +23567,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N290" s="2" t="inlineStr"/>
-      <c r="O290" s="3" t="inlineStr"/>
+      <c r="N290" s="2" t="n"/>
+      <c r="O290" s="3" t="n"/>
       <c r="P290" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -23961,8 +23969,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N295" s="2" t="inlineStr"/>
-      <c r="O295" s="3" t="inlineStr"/>
+      <c r="N295" s="2" t="n"/>
+      <c r="O295" s="3" t="n"/>
       <c r="P295" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -24035,8 +24043,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N296" s="2" t="inlineStr"/>
-      <c r="O296" s="3" t="inlineStr"/>
+      <c r="N296" s="2" t="n"/>
+      <c r="O296" s="3" t="n"/>
       <c r="P296" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -24273,8 +24281,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N299" s="2" t="inlineStr"/>
-      <c r="O299" s="3" t="inlineStr"/>
+      <c r="N299" s="2" t="n"/>
+      <c r="O299" s="3" t="n"/>
       <c r="P299" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -24593,8 +24601,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N303" s="2" t="inlineStr"/>
-      <c r="O303" s="3" t="inlineStr"/>
+      <c r="N303" s="2" t="n"/>
+      <c r="O303" s="3" t="n"/>
       <c r="P303" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -24667,8 +24675,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N304" s="2" t="inlineStr"/>
-      <c r="O304" s="3" t="inlineStr"/>
+      <c r="N304" s="2" t="n"/>
+      <c r="O304" s="3" t="n"/>
       <c r="P304" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -24741,8 +24749,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N305" s="2" t="inlineStr"/>
-      <c r="O305" s="3" t="inlineStr"/>
+      <c r="N305" s="2" t="n"/>
+      <c r="O305" s="3" t="n"/>
       <c r="P305" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -25225,8 +25233,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N311" s="2" t="inlineStr"/>
-      <c r="O311" s="3" t="inlineStr"/>
+      <c r="N311" s="2" t="n"/>
+      <c r="O311" s="3" t="n"/>
       <c r="P311" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -25299,8 +25307,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N312" s="2" t="inlineStr"/>
-      <c r="O312" s="3" t="inlineStr"/>
+      <c r="N312" s="2" t="n"/>
+      <c r="O312" s="3" t="n"/>
       <c r="P312" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -25373,8 +25381,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N313" s="2" t="inlineStr"/>
-      <c r="O313" s="3" t="inlineStr"/>
+      <c r="N313" s="2" t="n"/>
+      <c r="O313" s="3" t="n"/>
       <c r="P313" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -25611,8 +25619,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N316" s="2" t="inlineStr"/>
-      <c r="O316" s="3" t="inlineStr"/>
+      <c r="N316" s="2" t="n"/>
+      <c r="O316" s="3" t="n"/>
       <c r="P316" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -26095,8 +26103,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N322" s="2" t="inlineStr"/>
-      <c r="O322" s="3" t="inlineStr"/>
+      <c r="N322" s="2" t="n"/>
+      <c r="O322" s="3" t="n"/>
       <c r="P322" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -26169,8 +26177,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N323" s="2" t="inlineStr"/>
-      <c r="O323" s="3" t="inlineStr"/>
+      <c r="N323" s="2" t="n"/>
+      <c r="O323" s="3" t="n"/>
       <c r="P323" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -26243,8 +26251,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N324" s="2" t="inlineStr"/>
-      <c r="O324" s="3" t="inlineStr"/>
+      <c r="N324" s="2" t="n"/>
+      <c r="O324" s="3" t="n"/>
       <c r="P324" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -26645,8 +26653,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N329" s="2" t="inlineStr"/>
-      <c r="O329" s="3" t="inlineStr"/>
+      <c r="N329" s="2" t="n"/>
+      <c r="O329" s="3" t="n"/>
       <c r="P329" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -26719,8 +26727,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N330" s="2" t="inlineStr"/>
-      <c r="O330" s="3" t="inlineStr"/>
+      <c r="N330" s="2" t="n"/>
+      <c r="O330" s="3" t="n"/>
       <c r="P330" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -26793,8 +26801,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N331" s="2" t="inlineStr"/>
-      <c r="O331" s="3" t="inlineStr"/>
+      <c r="N331" s="2" t="n"/>
+      <c r="O331" s="3" t="n"/>
       <c r="P331" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -26867,8 +26875,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N332" s="2" t="inlineStr"/>
-      <c r="O332" s="3" t="inlineStr"/>
+      <c r="N332" s="2" t="n"/>
+      <c r="O332" s="3" t="n"/>
       <c r="P332" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -26941,8 +26949,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N333" s="2" t="inlineStr"/>
-      <c r="O333" s="3" t="inlineStr"/>
+      <c r="N333" s="2" t="n"/>
+      <c r="O333" s="3" t="n"/>
       <c r="P333" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -27671,8 +27679,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N342" s="2" t="inlineStr"/>
-      <c r="O342" s="3" t="inlineStr"/>
+      <c r="N342" s="2" t="n"/>
+      <c r="O342" s="3" t="n"/>
       <c r="P342" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -27745,8 +27753,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N343" s="2" t="inlineStr"/>
-      <c r="O343" s="3" t="inlineStr"/>
+      <c r="N343" s="2" t="n"/>
+      <c r="O343" s="3" t="n"/>
       <c r="P343" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -28065,8 +28073,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N347" s="2" t="inlineStr"/>
-      <c r="O347" s="3" t="inlineStr"/>
+      <c r="N347" s="2" t="n"/>
+      <c r="O347" s="3" t="n"/>
       <c r="P347" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -28139,8 +28147,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N348" s="2" t="inlineStr"/>
-      <c r="O348" s="3" t="inlineStr"/>
+      <c r="N348" s="2" t="n"/>
+      <c r="O348" s="3" t="n"/>
       <c r="P348" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -28377,8 +28385,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N351" s="2" t="inlineStr"/>
-      <c r="O351" s="3" t="inlineStr"/>
+      <c r="N351" s="2" t="n"/>
+      <c r="O351" s="3" t="n"/>
       <c r="P351" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -28943,8 +28951,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N358" s="2" t="inlineStr"/>
-      <c r="O358" s="3" t="inlineStr"/>
+      <c r="N358" s="2" t="n"/>
+      <c r="O358" s="3" t="n"/>
       <c r="P358" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -29017,8 +29025,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N359" s="2" t="inlineStr"/>
-      <c r="O359" s="3" t="inlineStr"/>
+      <c r="N359" s="2" t="n"/>
+      <c r="O359" s="3" t="n"/>
       <c r="P359" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -29091,8 +29099,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N360" s="2" t="inlineStr"/>
-      <c r="O360" s="3" t="inlineStr"/>
+      <c r="N360" s="2" t="n"/>
+      <c r="O360" s="3" t="n"/>
       <c r="P360" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -29165,8 +29173,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N361" s="2" t="inlineStr"/>
-      <c r="O361" s="3" t="inlineStr"/>
+      <c r="N361" s="2" t="n"/>
+      <c r="O361" s="3" t="n"/>
       <c r="P361" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -29239,8 +29247,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N362" s="2" t="inlineStr"/>
-      <c r="O362" s="3" t="inlineStr"/>
+      <c r="N362" s="2" t="n"/>
+      <c r="O362" s="3" t="n"/>
       <c r="P362" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -29313,8 +29321,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N363" s="2" t="inlineStr"/>
-      <c r="O363" s="3" t="inlineStr"/>
+      <c r="N363" s="2" t="n"/>
+      <c r="O363" s="3" t="n"/>
       <c r="P363" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -29633,8 +29641,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N367" s="2" t="inlineStr"/>
-      <c r="O367" s="3" t="inlineStr"/>
+      <c r="N367" s="2" t="n"/>
+      <c r="O367" s="3" t="n"/>
       <c r="P367" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -29707,8 +29715,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N368" s="2" t="inlineStr"/>
-      <c r="O368" s="3" t="inlineStr"/>
+      <c r="N368" s="2" t="n"/>
+      <c r="O368" s="3" t="n"/>
       <c r="P368" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -29781,8 +29789,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N369" s="2" t="inlineStr"/>
-      <c r="O369" s="3" t="inlineStr"/>
+      <c r="N369" s="2" t="n"/>
+      <c r="O369" s="3" t="n"/>
       <c r="P369" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -30101,8 +30109,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N373" s="2" t="inlineStr"/>
-      <c r="O373" s="3" t="inlineStr"/>
+      <c r="N373" s="2" t="n"/>
+      <c r="O373" s="3" t="n"/>
       <c r="P373" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -30175,8 +30183,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N374" s="2" t="inlineStr"/>
-      <c r="O374" s="3" t="inlineStr"/>
+      <c r="N374" s="2" t="n"/>
+      <c r="O374" s="3" t="n"/>
       <c r="P374" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -30249,8 +30257,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N375" s="2" t="inlineStr"/>
-      <c r="O375" s="3" t="inlineStr"/>
+      <c r="N375" s="2" t="n"/>
+      <c r="O375" s="3" t="n"/>
       <c r="P375" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -30323,8 +30331,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N376" s="2" t="inlineStr"/>
-      <c r="O376" s="3" t="inlineStr"/>
+      <c r="N376" s="2" t="n"/>
+      <c r="O376" s="3" t="n"/>
       <c r="P376" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -30397,8 +30405,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N377" s="2" t="inlineStr"/>
-      <c r="O377" s="3" t="inlineStr"/>
+      <c r="N377" s="2" t="n"/>
+      <c r="O377" s="3" t="n"/>
       <c r="P377" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -30471,8 +30479,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N378" s="2" t="inlineStr"/>
-      <c r="O378" s="3" t="inlineStr"/>
+      <c r="N378" s="2" t="n"/>
+      <c r="O378" s="3" t="n"/>
       <c r="P378" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -30873,8 +30881,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N383" s="2" t="inlineStr"/>
-      <c r="O383" s="3" t="inlineStr"/>
+      <c r="N383" s="2" t="n"/>
+      <c r="O383" s="3" t="n"/>
       <c r="P383" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -31029,8 +31037,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N385" s="2" t="inlineStr"/>
-      <c r="O385" s="3" t="inlineStr"/>
+      <c r="N385" s="2" t="n"/>
+      <c r="O385" s="3" t="n"/>
       <c r="P385" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -31185,8 +31193,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N387" s="2" t="inlineStr"/>
-      <c r="O387" s="3" t="inlineStr"/>
+      <c r="N387" s="2" t="n"/>
+      <c r="O387" s="3" t="n"/>
       <c r="P387" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -31259,8 +31267,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N388" s="2" t="inlineStr"/>
-      <c r="O388" s="3" t="inlineStr"/>
+      <c r="N388" s="2" t="n"/>
+      <c r="O388" s="3" t="n"/>
       <c r="P388" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -31825,8 +31833,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N395" s="2" t="inlineStr"/>
-      <c r="O395" s="3" t="inlineStr"/>
+      <c r="N395" s="2" t="n"/>
+      <c r="O395" s="3" t="n"/>
       <c r="P395" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -31899,8 +31907,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N396" s="2" t="inlineStr"/>
-      <c r="O396" s="3" t="inlineStr"/>
+      <c r="N396" s="2" t="n"/>
+      <c r="O396" s="3" t="n"/>
       <c r="P396" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -32137,8 +32145,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N399" s="2" t="inlineStr"/>
-      <c r="O399" s="3" t="inlineStr"/>
+      <c r="N399" s="2" t="n"/>
+      <c r="O399" s="3" t="n"/>
       <c r="P399" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -33359,8 +33367,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N414" s="2" t="inlineStr"/>
-      <c r="O414" s="3" t="inlineStr"/>
+      <c r="N414" s="2" t="n"/>
+      <c r="O414" s="3" t="n"/>
       <c r="P414" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -33433,8 +33441,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N415" s="2" t="inlineStr"/>
-      <c r="O415" s="3" t="inlineStr"/>
+      <c r="N415" s="2" t="n"/>
+      <c r="O415" s="3" t="n"/>
       <c r="P415" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -34491,8 +34499,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N428" s="2" t="inlineStr"/>
-      <c r="O428" s="3" t="inlineStr"/>
+      <c r="N428" s="2" t="n"/>
+      <c r="O428" s="3" t="n"/>
       <c r="P428" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -35385,8 +35393,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N439" s="2" t="inlineStr"/>
-      <c r="O439" s="3" t="inlineStr"/>
+      <c r="N439" s="2" t="n"/>
+      <c r="O439" s="3" t="n"/>
       <c r="P439" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -35869,8 +35877,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N445" s="2" t="inlineStr"/>
-      <c r="O445" s="3" t="inlineStr"/>
+      <c r="N445" s="2" t="n"/>
+      <c r="O445" s="3" t="n"/>
       <c r="P445" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -36189,8 +36197,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N449" s="2" t="inlineStr"/>
-      <c r="O449" s="3" t="inlineStr"/>
+      <c r="N449" s="2" t="n"/>
+      <c r="O449" s="3" t="n"/>
       <c r="P449" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -36509,8 +36517,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N453" s="2" t="inlineStr"/>
-      <c r="O453" s="3" t="inlineStr"/>
+      <c r="N453" s="2" t="n"/>
+      <c r="O453" s="3" t="n"/>
       <c r="P453" s="5" t="inlineStr">
         <is>
           <t>주의: 동명이인 중 임의 매칭</t>
@@ -40437,8 +40445,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N501" s="2" t="inlineStr"/>
-      <c r="O501" s="3" t="inlineStr"/>
+      <c r="N501" s="2" t="n"/>
+      <c r="O501" s="3" t="n"/>
       <c r="P501" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -41249,8 +41257,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N511" s="2" t="inlineStr"/>
-      <c r="O511" s="3" t="inlineStr"/>
+      <c r="N511" s="2" t="n"/>
+      <c r="O511" s="3" t="n"/>
       <c r="P511" s="5" t="inlineStr">
         <is>
           <t>주의: 동명이인 중 임의 매칭</t>
@@ -41487,8 +41495,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N514" s="2" t="inlineStr"/>
-      <c r="O514" s="3" t="inlineStr"/>
+      <c r="N514" s="2" t="n"/>
+      <c r="O514" s="3" t="n"/>
       <c r="P514" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -42053,8 +42061,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N521" s="2" t="inlineStr"/>
-      <c r="O521" s="3" t="inlineStr"/>
+      <c r="N521" s="2" t="n"/>
+      <c r="O521" s="3" t="n"/>
       <c r="P521" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -42127,8 +42135,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N522" s="2" t="inlineStr"/>
-      <c r="O522" s="3" t="inlineStr"/>
+      <c r="N522" s="2" t="n"/>
+      <c r="O522" s="3" t="n"/>
       <c r="P522" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -42201,8 +42209,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N523" s="2" t="inlineStr"/>
-      <c r="O523" s="3" t="inlineStr"/>
+      <c r="N523" s="2" t="n"/>
+      <c r="O523" s="3" t="n"/>
       <c r="P523" s="5" t="inlineStr">
         <is>
           <t>주의: 동명이인 중 임의 매칭</t>
@@ -42275,8 +42283,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N524" s="2" t="inlineStr"/>
-      <c r="O524" s="3" t="inlineStr"/>
+      <c r="N524" s="2" t="n"/>
+      <c r="O524" s="3" t="n"/>
       <c r="P524" s="5" t="inlineStr">
         <is>
           <t>주의: 동명이인 가능성</t>
@@ -42349,8 +42357,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N525" s="2" t="inlineStr"/>
-      <c r="O525" s="3" t="inlineStr"/>
+      <c r="N525" s="2" t="n"/>
+      <c r="O525" s="3" t="n"/>
       <c r="P525" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -42423,8 +42431,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N526" s="2" t="inlineStr"/>
-      <c r="O526" s="3" t="inlineStr"/>
+      <c r="N526" s="2" t="n"/>
+      <c r="O526" s="3" t="n"/>
       <c r="P526" s="5" t="inlineStr">
         <is>
           <t>주의: 동명이인 가능성</t>
@@ -42497,8 +42505,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N527" s="2" t="inlineStr"/>
-      <c r="O527" s="3" t="inlineStr"/>
+      <c r="N527" s="2" t="n"/>
+      <c r="O527" s="3" t="n"/>
       <c r="P527" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -42571,8 +42579,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N528" s="2" t="inlineStr"/>
-      <c r="O528" s="3" t="inlineStr"/>
+      <c r="N528" s="2" t="n"/>
+      <c r="O528" s="3" t="n"/>
       <c r="P528" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -42645,8 +42653,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N529" s="2" t="inlineStr"/>
-      <c r="O529" s="3" t="inlineStr"/>
+      <c r="N529" s="2" t="n"/>
+      <c r="O529" s="3" t="n"/>
       <c r="P529" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -42719,8 +42727,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N530" s="2" t="inlineStr"/>
-      <c r="O530" s="3" t="inlineStr"/>
+      <c r="N530" s="2" t="n"/>
+      <c r="O530" s="3" t="n"/>
       <c r="P530" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -42793,8 +42801,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N531" s="2" t="inlineStr"/>
-      <c r="O531" s="3" t="inlineStr"/>
+      <c r="N531" s="2" t="n"/>
+      <c r="O531" s="3" t="n"/>
       <c r="P531" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -42867,8 +42875,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N532" s="2" t="inlineStr"/>
-      <c r="O532" s="3" t="inlineStr"/>
+      <c r="N532" s="2" t="n"/>
+      <c r="O532" s="3" t="n"/>
       <c r="P532" s="5" t="inlineStr">
         <is>
           <t>주의: 동명이인 중 임의 매칭</t>
@@ -42941,8 +42949,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N533" s="2" t="inlineStr"/>
-      <c r="O533" s="3" t="inlineStr"/>
+      <c r="N533" s="2" t="n"/>
+      <c r="O533" s="3" t="n"/>
       <c r="P533" s="5" t="inlineStr">
         <is>
           <t>주의: 동명이인 중 임의 매칭</t>
@@ -43015,8 +43023,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N534" s="2" t="inlineStr"/>
-      <c r="O534" s="3" t="inlineStr"/>
+      <c r="N534" s="2" t="n"/>
+      <c r="O534" s="3" t="n"/>
       <c r="P534" s="5" t="inlineStr">
         <is>
           <t>주의: 동명이인 중 임의 매칭</t>
@@ -43089,8 +43097,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N535" s="2" t="inlineStr"/>
-      <c r="O535" s="3" t="inlineStr"/>
+      <c r="N535" s="2" t="n"/>
+      <c r="O535" s="3" t="n"/>
       <c r="P535" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -43163,8 +43171,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N536" s="2" t="inlineStr"/>
-      <c r="O536" s="3" t="inlineStr"/>
+      <c r="N536" s="2" t="n"/>
+      <c r="O536" s="3" t="n"/>
       <c r="P536" s="5" t="inlineStr">
         <is>
           <t>주의: 동명이인 중 임의 매칭</t>
@@ -43237,8 +43245,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N537" s="2" t="inlineStr"/>
-      <c r="O537" s="3" t="inlineStr"/>
+      <c r="N537" s="2" t="n"/>
+      <c r="O537" s="3" t="n"/>
       <c r="P537" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -43311,8 +43319,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N538" s="2" t="inlineStr"/>
-      <c r="O538" s="3" t="inlineStr"/>
+      <c r="N538" s="2" t="n"/>
+      <c r="O538" s="3" t="n"/>
       <c r="P538" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -43385,8 +43393,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N539" s="2" t="inlineStr"/>
-      <c r="O539" s="3" t="inlineStr"/>
+      <c r="N539" s="2" t="n"/>
+      <c r="O539" s="3" t="n"/>
       <c r="P539" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -43459,8 +43467,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N540" s="2" t="inlineStr"/>
-      <c r="O540" s="3" t="inlineStr"/>
+      <c r="N540" s="2" t="n"/>
+      <c r="O540" s="3" t="n"/>
       <c r="P540" s="5" t="inlineStr">
         <is>
           <t>미검색</t>
@@ -43533,8 +43541,8 @@
           <t>X</t>
         </is>
       </c>
-      <c r="N541" s="2" t="inlineStr"/>
-      <c r="O541" s="3" t="inlineStr"/>
+      <c r="N541" s="2" t="n"/>
+      <c r="O541" s="3" t="n"/>
       <c r="P541" s="5" t="inlineStr">
         <is>
           <t>파명/부친 불일치</t>
@@ -43607,8 +43615,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N542" s="2" t="inlineStr"/>
-      <c r="O542" s="3" t="inlineStr"/>
+      <c r="N542" s="2" t="n"/>
+      <c r="O542" s="3" t="n"/>
       <c r="P542" s="5" t="inlineStr">
         <is>
           <t>온라인 미등재 (현대 최신 직계자손)</t>
@@ -43681,8 +43689,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N543" s="2" t="inlineStr"/>
-      <c r="O543" s="3" t="inlineStr"/>
+      <c r="N543" s="2" t="n"/>
+      <c r="O543" s="3" t="n"/>
       <c r="P543" s="5" t="inlineStr">
         <is>
           <t>온라인 미등재 (현대 최신 직계자손)</t>
@@ -43755,8 +43763,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N544" s="2" t="inlineStr"/>
-      <c r="O544" s="3" t="inlineStr"/>
+      <c r="N544" s="2" t="n"/>
+      <c r="O544" s="3" t="n"/>
       <c r="P544" s="5" t="inlineStr">
         <is>
           <t>온라인 미등재 (현대 최신 직계자손)</t>
@@ -43829,8 +43837,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N545" s="2" t="inlineStr"/>
-      <c r="O545" s="3" t="inlineStr"/>
+      <c r="N545" s="2" t="n"/>
+      <c r="O545" s="3" t="n"/>
       <c r="P545" s="5" t="inlineStr">
         <is>
           <t>온라인 미등재 (현대 최신 직계자손)</t>
@@ -43903,8 +43911,8 @@
           <t>O</t>
         </is>
       </c>
-      <c r="N546" s="2" t="inlineStr"/>
-      <c r="O546" s="3" t="inlineStr"/>
+      <c r="N546" s="2" t="n"/>
+      <c r="O546" s="3" t="n"/>
       <c r="P546" s="5" t="inlineStr">
         <is>
           <t>온라인 미등재 (현대 최신 직계자손)</t>
